--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56832278</v>
+        <v>56832247</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lappkärrsmossen, S, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558906.6489465655</v>
+        <v>558907</v>
       </c>
       <c r="R2" t="n">
-        <v>6625997.958885567</v>
+        <v>6625998</v>
       </c>
       <c r="S2" t="n">
         <v>98</v>
@@ -750,19 +746,9 @@
           <t>2016-02-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-02-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,15 +775,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56832247</v>
+        <v>72643208</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,22 +804,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappkärrsmossen, S, Vstm</t>
+          <t>Lappkärrsmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558906.6489465655</v>
+        <v>558916</v>
       </c>
       <c r="R3" t="n">
-        <v>6625997.958885567</v>
+        <v>6626048</v>
       </c>
       <c r="S3" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-02-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-02-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +860,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,12 +875,7 @@
         <v>56832250</v>
       </c>
       <c r="B4" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558906.6489465655</v>
+        <v>558907</v>
       </c>
       <c r="R4" t="n">
-        <v>6625997.958885567</v>
+        <v>6625998</v>
       </c>
       <c r="S4" t="n">
         <v>98</v>
@@ -980,19 +943,9 @@
           <t>2016-02-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-02-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72643208</v>
+        <v>56832278</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,37 +983,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappkärrsmossen, Vstm</t>
+          <t>Lappkärrsmossen, S, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558915.9506910068</v>
+        <v>558907</v>
       </c>
       <c r="R5" t="n">
-        <v>6626047.981196136</v>
+        <v>6625998</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-02-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-02-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,15 +1059,622 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>68881774</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Usträngsbo Nyckelbiotop, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558892</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626069</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-01-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-01-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>98549776</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Utsträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558961</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6625943</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>98550091</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Utsträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558961</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6625943</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110818359</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558895</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6625916</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blomrika vägkanter</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110818386</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558895</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6625916</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blomrika vägkanter</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56832247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72643208</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56832250</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56832278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1194,6 +1219,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68881774</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98549776</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98550091</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110818359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,8 +1720,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110818386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>